--- a/final_data_pipeline/output/311615longform_elec_options.xlsx
+++ b/final_data_pipeline/output/311615longform_elec_options.xlsx
@@ -672,7 +672,7 @@
         <v>68</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="L2">
         <v>8000</v>
@@ -719,7 +719,7 @@
         <v>68</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="L3">
         <v>8000</v>
@@ -766,7 +766,7 @@
         <v>68</v>
       </c>
       <c r="K4">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="L4">
         <v>8000</v>
@@ -1095,7 +1095,7 @@
         <v>68</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L11">
         <v>8000</v>
@@ -1142,7 +1142,7 @@
         <v>68</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L12">
         <v>8000</v>
@@ -1189,7 +1189,7 @@
         <v>68</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="L13">
         <v>8000</v>
@@ -1283,7 +1283,7 @@
         <v>68</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="L15">
         <v>8000</v>
@@ -1377,7 +1377,7 @@
         <v>68</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L17">
         <v>8000</v>
@@ -1424,7 +1424,7 @@
         <v>68</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L18">
         <v>8000</v>
@@ -1471,7 +1471,7 @@
         <v>68</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L19">
         <v>8000</v>
@@ -1518,7 +1518,7 @@
         <v>68</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L20">
         <v>8000</v>
@@ -1565,7 +1565,7 @@
         <v>68</v>
       </c>
       <c r="K21">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="L21">
         <v>8000</v>
@@ -1659,7 +1659,7 @@
         <v>68</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="L23">
         <v>8000</v>
@@ -1941,7 +1941,7 @@
         <v>68</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="L29">
         <v>8000</v>
@@ -2035,7 +2035,7 @@
         <v>68</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="L31">
         <v>8000</v>
@@ -2082,7 +2082,7 @@
         <v>69</v>
       </c>
       <c r="K32">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="L32">
         <v>8000</v>
@@ -2097,10 +2097,10 @@
         <v>28.03121167607779</v>
       </c>
       <c r="R32">
-        <v>1.441896551724138</v>
+        <v>1.466311090415359</v>
       </c>
       <c r="S32">
-        <v>1.530185185185185</v>
+        <v>1.558048815385048</v>
       </c>
       <c r="T32">
         <v>0.003503901459509723</v>
@@ -2135,7 +2135,7 @@
         <v>68</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="L33">
         <v>8000</v>
